--- a/Tasks_list.xlsx
+++ b/Tasks_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -26,6 +26,9 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Comments</t>
+  </si>
+  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -33,6 +36,28 @@
   </si>
   <si>
     <t>AV</t>
+  </si>
+  <si>
+    <t>Notes updated</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t xml:space="preserve">Better and updated: </t>
+    </r>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="14"/>
+        <rFont val="Helvetica Neue"/>
+      </rPr>
+      <t>https://www.nature.com/articles/s41597-025-05374-1?fromPaywallRec=false</t>
+    </r>
   </si>
   <si>
     <t>Search for on field high resolution data for any other district /State</t>
@@ -86,7 +111,7 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="ddd, d mmm yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -106,6 +131,12 @@
       <b val="1"/>
       <sz val="10"/>
       <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color indexed="14"/>
       <name val="Helvetica Neue"/>
     </font>
     <font>
@@ -164,12 +195,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="14"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor indexed="15"/>
         <bgColor auto="1"/>
       </patternFill>
@@ -177,6 +202,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="16"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -370,7 +401,7 @@
     <xf numFmtId="59" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -400,25 +431,25 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="7" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -449,6 +480,7 @@
       <rgbColor rgb="ff3f3f3f"/>
       <rgbColor rgb="ffdbdbdb"/>
       <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff0000ff"/>
       <rgbColor rgb="ff00a2ff"/>
       <rgbColor rgb="ffcadfff"/>
       <rgbColor rgb="ffe6efff"/>
@@ -1483,13 +1515,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="7.35156" style="1" customWidth="1"/>
     <col min="2" max="2" width="54.625" style="1" customWidth="1"/>
-    <col min="3" max="5" width="16.3516" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="3" max="4" width="16.3516" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.4688" style="1" customWidth="1"/>
+    <col min="6" max="6" width="47.2109" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1">
@@ -1508,109 +1542,123 @@
       <c r="E1" t="s" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" ht="20.25" customHeight="1">
+      <c r="F1" t="s" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="40.3" customHeight="1">
       <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" t="s" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="7">
         <v>45847</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s" s="8">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" ht="20.05" customHeight="1">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" t="s" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s" s="11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" s="12">
         <v>45847</v>
       </c>
       <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s" s="11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="12">
         <v>45847</v>
       </c>
       <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" ht="26.7" customHeight="1">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" t="s" s="10">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s" s="11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" s="12">
         <v>45847</v>
       </c>
       <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" ht="20.05" customHeight="1">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="12">
         <v>45847</v>
       </c>
       <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
     </row>
     <row r="7" ht="20.05" customHeight="1">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s" s="11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" s="12">
         <v>45847</v>
       </c>
       <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
     </row>
     <row r="8" ht="20.05" customHeight="1">
       <c r="A8" s="14"/>
       <c r="B8" t="s" s="10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s" s="11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D8" s="12">
         <v>45847</v>
       </c>
       <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" ht="20.05" customHeight="1">
       <c r="A9" s="14"/>
@@ -1618,6 +1666,7 @@
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" ht="20.05" customHeight="1">
       <c r="A10" s="14"/>
@@ -1625,6 +1674,7 @@
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" ht="20.05" customHeight="1">
       <c r="A11" s="14"/>
@@ -1632,6 +1682,7 @@
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" ht="20.05" customHeight="1">
       <c r="A12" s="14"/>
@@ -1639,6 +1690,7 @@
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
       <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" ht="20.05" customHeight="1">
       <c r="A13" s="14"/>
@@ -1646,6 +1698,7 @@
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
     </row>
     <row r="14" ht="20.05" customHeight="1">
       <c r="A14" s="14"/>
@@ -1653,6 +1706,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" ht="20.05" customHeight="1">
       <c r="A15" s="14"/>
@@ -1660,6 +1714,7 @@
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" ht="20.05" customHeight="1">
       <c r="A16" s="14"/>
@@ -1667,6 +1722,7 @@
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
       <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" ht="20.05" customHeight="1">
       <c r="A17" s="14"/>
@@ -1674,6 +1730,7 @@
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
       <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
     </row>
     <row r="18" ht="20.05" customHeight="1">
       <c r="A18" s="14"/>
@@ -1681,6 +1738,7 @@
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
     </row>
     <row r="19" ht="20.05" customHeight="1">
       <c r="A19" s="14"/>
@@ -1688,6 +1746,7 @@
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
       <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
     </row>
     <row r="20" ht="20.05" customHeight="1">
       <c r="A20" s="14"/>
@@ -1695,6 +1754,7 @@
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
     </row>
     <row r="21" ht="20.05" customHeight="1">
       <c r="A21" s="14"/>
@@ -1702,6 +1762,7 @@
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
       <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" ht="20.05" customHeight="1">
       <c r="A22" s="14"/>
@@ -1709,8 +1770,12 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" location="" tooltip="" display="https://www.nature.com/articles/s41597-025-05374-1?fromPaywallRec=false"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
@@ -1737,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="18">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="23.7" customHeight="1">
@@ -1745,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s" s="20">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -1753,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s" s="22">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -1761,7 +1826,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="23">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -1769,7 +1834,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="22">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -1777,7 +1842,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="23">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="12.7" customHeight="1">
